--- a/data/GPS/Metricas_GPS7.xlsx
+++ b/data/GPS/Metricas_GPS7.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30506"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_2070CB3775220E96AE6CCF3ADD1E570FE97B8056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -134,25 +143,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -163,41 +173,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -205,7 +217,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -395,22 +407,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -419,21 +434,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,12 +496,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B2" s="1">
-        <v>144.817</v>
+        <v>144.81700000000001</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
@@ -500,39 +516,39 @@
         <v>0.219</v>
       </c>
       <c r="G2" s="1">
-        <v>0.036</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="H2" s="1">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="I2" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="K2" s="1">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1">
-        <v>5.243</v>
+        <v>5.2430000000000003</v>
       </c>
       <c r="M2" s="1">
-        <v>-6.082</v>
+        <v>-6.0819999999999999</v>
       </c>
       <c r="N2" s="1">
         <v>29.21</v>
       </c>
       <c r="O2" s="1">
-        <v>839.392</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>839.39200000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B3" s="1">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -541,45 +557,45 @@
         <v>21</v>
       </c>
       <c r="E3" s="1">
-        <v>6.478</v>
+        <v>6.4779999999999998</v>
       </c>
       <c r="F3" s="1">
-        <v>0.238</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="G3" s="1">
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="H3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="K3" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="L3" s="1">
-        <v>4.204</v>
+        <v>4.2039999999999997</v>
       </c>
       <c r="M3" s="1">
-        <v>-4.932</v>
+        <v>-4.9320000000000004</v>
       </c>
       <c r="N3" s="1">
-        <v>26.647</v>
+        <v>26.646999999999998</v>
       </c>
       <c r="O3" s="1">
         <v>1426.422</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B4" s="1">
-        <v>144.633</v>
+        <v>144.63300000000001</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
@@ -588,42 +604,42 @@
         <v>21</v>
       </c>
       <c r="E4" s="1">
-        <v>6.655</v>
+        <v>6.6550000000000002</v>
       </c>
       <c r="F4" s="1">
         <v>0.47</v>
       </c>
       <c r="G4" s="1">
-        <v>0.022</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="H4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="1">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="L4" s="1">
-        <v>5.104</v>
+        <v>5.1040000000000001</v>
       </c>
       <c r="M4" s="1">
-        <v>-5.084</v>
+        <v>-5.0839999999999996</v>
       </c>
       <c r="N4" s="1">
         <v>28.238</v>
       </c>
       <c r="O4" s="1">
-        <v>998.349</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>998.34900000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B5" s="1">
         <v>147.5</v>
@@ -635,47 +651,47 @@
         <v>19</v>
       </c>
       <c r="E5" s="1">
-        <v>8.394</v>
+        <v>8.3940000000000001</v>
       </c>
       <c r="F5" s="1">
         <v>0.63</v>
       </c>
       <c r="G5" s="1">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="1">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="K5" s="1">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="L5" s="1">
-        <v>4.988</v>
+        <v>4.9880000000000004</v>
       </c>
       <c r="M5" s="1">
-        <v>-5.793</v>
+        <v>-5.7930000000000001</v>
       </c>
       <c r="N5" s="1">
-        <v>27.691</v>
+        <v>27.690999999999999</v>
       </c>
       <c r="O5" s="1">
-        <v>1672.985</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>1672.9849999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B6" s="1">
         <v>143.083</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -688,36 +704,36 @@
         <v>1.073</v>
       </c>
       <c r="G6" s="1">
-        <v>0.167</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="I6" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="J6" s="1">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="K6" s="1">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="L6" s="1">
         <v>5.242</v>
       </c>
       <c r="M6" s="1">
-        <v>-5.957</v>
+        <v>-5.9569999999999999</v>
       </c>
       <c r="N6" s="1">
-        <v>32.479</v>
+        <v>32.478999999999999</v>
       </c>
       <c r="O6" s="1">
-        <v>2361.385</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>2361.3850000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B7" s="1">
         <v>149.35</v>
@@ -729,139 +745,139 @@
         <v>25</v>
       </c>
       <c r="E7" s="1">
-        <v>5.229</v>
+        <v>5.2290000000000001</v>
       </c>
       <c r="F7" s="1">
-        <v>0.461</v>
+        <v>0.46100000000000002</v>
       </c>
       <c r="G7" s="1">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="K7" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="L7" s="1">
         <v>4.851</v>
       </c>
       <c r="M7" s="1">
-        <v>-6.969</v>
+        <v>-6.9690000000000003</v>
       </c>
       <c r="N7" s="1">
-        <v>27.684</v>
+        <v>27.684000000000001</v>
       </c>
       <c r="O7" s="1">
         <v>1188.577</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B8" s="1">
-        <v>144.717</v>
-      </c>
-      <c r="C8" s="4" t="s">
+        <v>144.71700000000001</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="1">
-        <v>9.503</v>
+        <v>9.5030000000000001</v>
       </c>
       <c r="F8" s="1">
-        <v>0.817</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="G8" s="1">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="H8" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="J8" s="1">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="K8" s="1">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="L8" s="1">
         <v>6.29</v>
       </c>
       <c r="M8" s="1">
-        <v>-5.256</v>
+        <v>-5.2560000000000002</v>
       </c>
       <c r="N8" s="1">
-        <v>28.231</v>
+        <v>28.231000000000002</v>
       </c>
       <c r="O8" s="1">
         <v>2042.16</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B9" s="1">
-        <v>80.85</v>
-      </c>
-      <c r="C9" s="4" t="s">
+        <v>80.849999999999994</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="1">
-        <v>5.863</v>
+        <v>5.8630000000000004</v>
       </c>
       <c r="F9" s="1">
-        <v>0.277</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="G9" s="1">
         <v>0.05</v>
       </c>
       <c r="H9" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J9" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="K9" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="L9" s="1">
-        <v>5.256</v>
+        <v>5.2560000000000002</v>
       </c>
       <c r="M9" s="1">
-        <v>-6.321</v>
+        <v>-6.3209999999999997</v>
       </c>
       <c r="N9" s="1">
-        <v>28.426</v>
+        <v>28.425999999999998</v>
       </c>
       <c r="O9" s="1">
-        <v>1090.887</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>1090.8869999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B10" s="1">
-        <v>146.633</v>
+        <v>146.63300000000001</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
@@ -873,89 +889,89 @@
         <v>4.819</v>
       </c>
       <c r="F10" s="1">
-        <v>0.352</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="G10" s="1">
-        <v>0.058</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="H10" s="1">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="I10" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="J10" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="K10" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="L10" s="1">
         <v>6.931</v>
       </c>
       <c r="M10" s="1">
-        <v>-7.436</v>
+        <v>-7.4359999999999999</v>
       </c>
       <c r="N10" s="1">
-        <v>31.813</v>
+        <v>31.812999999999999</v>
       </c>
       <c r="O10" s="1">
         <v>1158.559</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B11" s="1">
         <v>115.217</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="1">
-        <v>8.855</v>
+        <v>8.8550000000000004</v>
       </c>
       <c r="F11" s="1">
-        <v>0.295</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="G11" s="1">
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="H11" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="1">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="K11" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="L11" s="1">
         <v>4.66</v>
       </c>
       <c r="M11" s="1">
-        <v>-4.933</v>
+        <v>-4.9329999999999998</v>
       </c>
       <c r="N11" s="1">
-        <v>27.986</v>
+        <v>27.986000000000001</v>
       </c>
       <c r="O11" s="1">
         <v>2098.299</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B12" s="1">
-        <v>86.083</v>
+        <v>86.082999999999998</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>33</v>
@@ -970,36 +986,36 @@
         <v>0.221</v>
       </c>
       <c r="G12" s="1">
-        <v>0.021</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="K12" s="1">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="L12" s="1">
-        <v>4.684</v>
+        <v>4.6840000000000002</v>
       </c>
       <c r="M12" s="1">
-        <v>-4.794</v>
+        <v>-4.7939999999999996</v>
       </c>
       <c r="N12" s="1">
-        <v>28.321</v>
+        <v>28.321000000000002</v>
       </c>
       <c r="O12" s="1">
-        <v>1104.334</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>1104.3340000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B13" s="1">
         <v>144.75</v>
@@ -1011,31 +1027,31 @@
         <v>32</v>
       </c>
       <c r="E13" s="1">
-        <v>10.095</v>
+        <v>10.095000000000001</v>
       </c>
       <c r="F13" s="1">
-        <v>0.943</v>
+        <v>0.94299999999999995</v>
       </c>
       <c r="G13" s="1">
         <v>0.05</v>
       </c>
       <c r="H13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J13" s="1">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="K13" s="1">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="L13" s="1">
         <v>4.99</v>
       </c>
       <c r="M13" s="1">
-        <v>-5.801</v>
+        <v>-5.8010000000000002</v>
       </c>
       <c r="N13" s="1">
         <v>28.102</v>
@@ -1044,106 +1060,106 @@
         <v>2154.114</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B14" s="1">
-        <v>142.433</v>
-      </c>
-      <c r="C14" s="4" t="s">
+        <v>142.43299999999999</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="1">
-        <v>5.589</v>
+        <v>5.5890000000000004</v>
       </c>
       <c r="F14" s="1">
-        <v>0.589</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="G14" s="1">
-        <v>0.086</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="H14" s="1">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="I14" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="J14" s="1">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="K14" s="1">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="L14" s="1">
-        <v>8.979</v>
+        <v>8.9789999999999992</v>
       </c>
       <c r="M14" s="1">
         <v>-10.238</v>
       </c>
       <c r="N14" s="1">
-        <v>28.807</v>
+        <v>28.806999999999999</v>
       </c>
       <c r="O14" s="1">
         <v>1582.076</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B15" s="1">
-        <v>90.783</v>
-      </c>
-      <c r="C15" s="4" t="s">
+        <v>90.783000000000001</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="1">
-        <v>6.058</v>
+        <v>6.0579999999999998</v>
       </c>
       <c r="F15" s="1">
-        <v>0.297</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="G15" s="1">
-        <v>0.073</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="H15" s="1">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="I15" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="K15" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L15" s="1">
-        <v>4.503</v>
+        <v>4.5030000000000001</v>
       </c>
       <c r="M15" s="1">
-        <v>-5.557</v>
+        <v>-5.5570000000000004</v>
       </c>
       <c r="N15" s="1">
-        <v>29.614</v>
+        <v>29.614000000000001</v>
       </c>
       <c r="O15" s="1">
         <v>936.08</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>46256.0</v>
+        <v>46256</v>
       </c>
       <c r="B16" s="1">
-        <v>146.883</v>
+        <v>146.88300000000001</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>38</v>
@@ -1155,37 +1171,37 @@
         <v>6.05</v>
       </c>
       <c r="F16" s="1">
-        <v>0.302</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="G16" s="1">
-        <v>0.007</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H16" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="K16" s="1">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="L16" s="1">
-        <v>4.278</v>
+        <v>4.2779999999999996</v>
       </c>
       <c r="M16" s="1">
-        <v>-5.216</v>
+        <v>-5.2160000000000002</v>
       </c>
       <c r="N16" s="1">
-        <v>25.909</v>
+        <v>25.908999999999999</v>
       </c>
       <c r="O16" s="1">
-        <v>1078.935</v>
+        <v>1078.9349999999999</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>